--- a/jpcore-r4/develop/CodeSystem-jp-condition-disease-code-icd10-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-condition-disease-code-icd10-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-08-05</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>
